--- a/out/LSTM-mamba2_repeat_2_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_2_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.155749764472209</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.990389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.990389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.990389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.990389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.990389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.990389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.990389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.990389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.990389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.363781077531166e-05</v>
+        <v>-9.028927320521324e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08459570113556741</v>
+        <v>-0.1037250332593648</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.08473418674722127</v>
+        <v>-0.1038953169789104</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2331776667353797</v>
+        <v>0.2876418110555966</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3820693708612293</v>
+        <v>0.4719405879425919</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01661389638412946</v>
+        <v>0.02049438205934407</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1817449400060787</v>
+        <v>0.2248262053035155</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.02913498523280151</v>
+        <v>0.03594029158310495</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2233957265839446</v>
+        <v>0.2762054937622342</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03539587802993697</v>
+        <v>0.04366320975871988</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.265049468537922</v>
+        <v>0.3275882019587611</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.009365503035067021</v>
+        <v>0.01155418788124789</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2483407039243672</v>
+        <v>0.3069779783840266</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.005201288651664769</v>
+        <v>0.006417104351165654</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2493700097963547</v>
+        <v>0.3082488606887963</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01093132641993218</v>
+        <v>0.01348698945083388</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2660385842566714</v>
+        <v>0.3288123602160108</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004291889219067836</v>
+        <v>0.005294658180000239</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2636809073773576</v>
+        <v>0.3259053062485033</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003055034929797509</v>
+        <v>0.003769158075759273</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2654972976417704</v>
+        <v>0.3281472705010839</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001199449493376043</v>
+        <v>0.001480532971537081</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2648387801370693</v>
+        <v>0.3273358735346063</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0006778460329851948</v>
+        <v>0.0008381530023541796</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2649958632924312</v>
+        <v>0.3275309646785506</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002557099692113423</v>
+        <v>0.0003167771692067918</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2648273486720382</v>
+        <v>0.3273241493362637</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001172066092191951</v>
+        <v>0.0001458315807480156</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2648058664731176</v>
+        <v>0.3272988064421003</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>3.940289118946859e-05</v>
+        <v>4.989812001607026e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2647681710284625</v>
+        <v>0.3272534524713112</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>8.355601046452064e-06</v>
+        <v>1.121751555640607e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2647446289386067</v>
+        <v>0.3272256063400598</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.677800523226032e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2647396185136182</v>
+        <v>0.3272205936811452</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-1.404168982957566e-06</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2647351274713219</v>
+        <v>0.3272162480553358</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.908363659633048e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2647314106408423</v>
+        <v>0.3272128977005431</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2647261148108381</v>
+        <v>0.3272075283735553</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2647204528138344</v>
+        <v>0.3272015356401249</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2647202690713752</v>
+        <v>0.3271961678515465</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2647203058198669</v>
+        <v>0.3271962046000382</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2647204160653425</v>
+        <v>0.3271963148455138</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2647204895623261</v>
+        <v>0.3271963883424974</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2647206733047853</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2647222167414418</v>
+        <v>0.327198115521613</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2647236866811148</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2647249361298368</v>
+        <v>0.3272008349100081</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2647262958240341</v>
+        <v>0.3272021946042054</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2647240909145249</v>
+        <v>0.3271999896946962</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2647236866811148</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2647228414658029</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2647233926931801</v>
+        <v>0.3271992914733514</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2647230619567537</v>
+        <v>0.327198960736925</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2647227679688192</v>
+        <v>0.3271986667489906</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2647228414658029</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2647224004839009</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2647222902384254</v>
+        <v>0.3271981890185967</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>2.590389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2647222534899337</v>
+        <v>0.327198152270105</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2647224004839009</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2647219227535073</v>
+        <v>0.3271978215336785</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2647228782142946</v>
+        <v>0.3271987769944659</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2647228414658029</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2647225107293765</v>
+        <v>0.3271984095095478</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.990389075499146</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2647229517112784</v>
+        <v>0.3271988504914497</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2647223269869173</v>
+        <v>0.3271982257670886</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2647221432444581</v>
+        <v>0.3271980420246294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2647217390110481</v>
+        <v>0.3271976377912194</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2647208937957362</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2647208570472445</v>
+        <v>0.3271967558274158</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2647210040412117</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2647209305442281</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2647210040412117</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2647210407897036</v>
+        <v>0.3271969395698749</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2647209305442281</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.26472137152613</v>
+        <v>0.3271972703063013</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2647212612806545</v>
+        <v>0.3271971600608258</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2647212245321625</v>
+        <v>0.3271971233123338</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2647211510351789</v>
+        <v>0.3271970498153502</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2647211142866872</v>
+        <v>0.3271970130668585</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2647208937957362</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2647208202987525</v>
+        <v>0.3271967190789238</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2647207468017689</v>
+        <v>0.3271966455819402</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2647207835502608</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2647206733047853</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2647207835502608</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2647210775381953</v>
+        <v>0.3271969763183666</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_2_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_2_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.990389075499146</v>
+        <v>0.8114350597773905</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.990389075499146</v>
+        <v>1.5305525089137</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.990389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.990389075499146</v>
+        <v>1.5305525089137</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.990389075499146</v>
+        <v>1.5305525089137</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.990389075499146</v>
+        <v>1.5305525089137</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.990389075499146</v>
+        <v>0.8114350597773907</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.990389075499146</v>
+        <v>0.8114350597773907</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.990389075499146</v>
+        <v>1.5305525089137</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC45" t="n">
-        <v>-7.363781077531166e-05</v>
+        <v>-8.570292203873397e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.08459570113556741</v>
+        <v>-0.09845619665895525</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.09854189958099392</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.09854189958099392</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.09854189958099392</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.09854189958099392</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.09854189958099392</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.09854189958099392</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.09854189958099392</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.09854189958099392</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.09854189958099392</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.09854189958099392</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.09854189958099392</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.09854189958099392</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.0846693389463427</v>
+        <v>-0.09854189958099392</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.08473418674722127</v>
+        <v>-0.09861779246388865</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2331776667353797</v>
+        <v>0.2728932662517455</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3820693708612293</v>
+        <v>0.4476932195827002</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01661389638412946</v>
+        <v>0.01944362451114522</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1817449400060787</v>
+        <v>0.2132489372843481</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.02913498523280151</v>
+        <v>0.0340973642194692</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2233957265839446</v>
+        <v>0.261993809362548</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03539587802993697</v>
+        <v>0.04142458244643064</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.265049468537922</v>
+        <v>0.310742108989852</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.009365503035067021</v>
+        <v>0.0109615360033033</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2483407039243672</v>
+        <v>0.2911883221077285</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.005201288651664769</v>
+        <v>0.006088019655193326</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2493700097963547</v>
+        <v>0.2923937901453558</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01093132641993218</v>
+        <v>0.01279489493884663</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2660385842566714</v>
+        <v>0.3119021935583558</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004291889219067836</v>
+        <v>0.005023377688153793</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2636809073773576</v>
+        <v>0.3091440046060139</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003055034929797509</v>
+        <v>0.003575965340619859</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2654972976417704</v>
+        <v>0.3112704624351687</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001199449493376043</v>
+        <v>0.001404491064401727</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2648387801370693</v>
+        <v>0.3105006922323729</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0006778460329851948</v>
+        <v>0.0007949934336779145</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2649958632924312</v>
+        <v>0.3106853667138552</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002557099692113423</v>
+        <v>0.000299161630746566</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2648273486720382</v>
+        <v>0.3104892321718118</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001172066092191951</v>
+        <v>0.0001381248576441024</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2648058664731176</v>
+        <v>0.3104649286955984</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>3.940289118946859e-05</v>
+        <v>4.747614413300833e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2647681710284625</v>
+        <v>0.3104216360649285</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>8.355601046452064e-06</v>
+        <v>1.026354405308807e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2647446289386067</v>
+        <v>0.3103951143686669</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.677800523226032e-06</v>
+        <v>2.631772026544036e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2647396185136182</v>
+        <v>0.3103901024543941</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-1.404168982957566e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2647351274713219</v>
+        <v>0.3103857208688334</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.908363659633048e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2647314106408423</v>
+        <v>0.3103823705140406</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2647261148108381</v>
+        <v>0.3103770011870528</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2647204528138344</v>
+        <v>0.3103710084536225</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2647202690713752</v>
+        <v>0.3103656406650441</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2647203058198669</v>
+        <v>0.3103656774135358</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2647204160653425</v>
+        <v>0.3103657876590113</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2647204895623261</v>
+        <v>0.310365861155995</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.590389075499146</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2647206733047853</v>
+        <v>0.3103660448984541</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5557497644722087</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2647222167414418</v>
+        <v>0.3103675883351106</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2647236866811148</v>
+        <v>0.3103690582747837</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2647249361298368</v>
+        <v>0.3103703077235057</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2647262958240341</v>
+        <v>0.3103716674177029</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2647240909145249</v>
+        <v>0.3103694625081937</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2647236866811148</v>
+        <v>0.3103690582747837</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2647228414658029</v>
+        <v>0.3103682130594717</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2647233926931801</v>
+        <v>0.310368764286849</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2647230619567537</v>
+        <v>0.3103684335504225</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2647227679688192</v>
+        <v>0.310368139562488</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2647228414658029</v>
+        <v>0.3103682130594717</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2647224004839009</v>
+        <v>0.3103677720775697</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.590389075499146</v>
+        <v>1.7305525089137</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2647222902384254</v>
+        <v>0.3103676618320942</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>2.590389075499146</v>
+        <v>1.011435059777391</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2647222534899337</v>
+        <v>0.3103676250836025</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5557497644722087</v>
+        <v>0.2923176106410809</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2647224004839009</v>
+        <v>0.3103677720775697</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.4267998384952287</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2647219227535073</v>
+        <v>0.3103672943471761</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2647228782142946</v>
+        <v>0.3103682498079634</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2647228414658029</v>
+        <v>0.3103682130594717</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108085</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2647225107293765</v>
+        <v>0.3103678823230453</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.990389075499146</v>
+        <v>0.09231761064108088</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2647229517112784</v>
+        <v>0.3103683233049472</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.155749764472209</v>
+        <v>0.09231761064108088</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2647223269869173</v>
+        <v>0.3103676985805861</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5557497644722087</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2647221432444581</v>
+        <v>0.310367514838127</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2647217390110481</v>
+        <v>0.3103671106047169</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2647208937957362</v>
+        <v>0.310366265389405</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2647208570472445</v>
+        <v>0.3103662286409133</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2647210040412117</v>
+        <v>0.3103663756348805</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2647209305442281</v>
+        <v>0.3103663021378969</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2647210040412117</v>
+        <v>0.3103663756348805</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2647210407897036</v>
+        <v>0.3103664123833724</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2647209305442281</v>
+        <v>0.3103663021378969</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.26472137152613</v>
+        <v>0.3103667431197988</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2647212612806545</v>
+        <v>0.3103666328743233</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2647212245321625</v>
+        <v>0.3103665961258313</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2647211510351789</v>
+        <v>0.3103665226288477</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2647211142866872</v>
+        <v>0.310366485880356</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2647208937957362</v>
+        <v>0.310366265389405</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2647208202987525</v>
+        <v>0.3103661918924213</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2647207468017689</v>
+        <v>0.3103661183954377</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2647207835502608</v>
+        <v>0.3103661551439296</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2647206733047853</v>
+        <v>0.3103660448984541</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2647207835502608</v>
+        <v>0.3103661551439296</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.155749764472209</v>
+        <v>-0.6267998384952288</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2647210775381953</v>
+        <v>0.3103664491318641</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-mamba2_repeat_2_000008.xlsx
+++ b/out/LSTM-mamba2_repeat_2_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.3490680456161499</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.2158145010471344</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.09491157531738281</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.06944103538990021</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.04264439642429352</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0154268778860569</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0005583725869655609</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.09231761064108085</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.002331789582967758</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.011435059777391</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.002492031082510948</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.003536805510520935</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.007855687290430069</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.006165312603116035</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.008848059922456741</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.7305525089137</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.008029982447624207</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.011435059777391</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.002011960372328758</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.09231761064108085</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.004438214004039764</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.09231761064108085</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.006270695477724075</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.8114350597773905</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.01320860162377357</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.5305525089137</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.01769386976957321</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.7305525089137</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.02054044231772423</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01987005397677422</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.02210205420851707</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.7305525089137</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.02121996879577637</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.7305525089137</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.02007980272173882</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.7305525089137</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.01499154418706894</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.7305525089137</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.01849984005093575</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.7305525089137</v>
+        <v>-0.16</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.01916822791099548</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.5305525089137</v>
+        <v>-0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.02093755081295967</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.5305525089137</v>
+        <v>-0.16</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01928172633051872</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.5305525089137</v>
+        <v>-0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.01616281270980835</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.8114350597773907</v>
+        <v>-0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.001094117760658264</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.09231761064108085</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.01025564596056938</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-3.56677919626236e-05</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.09231761064108085</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.004988983273506165</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.8114350597773907</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.004473280161619186</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.5305525089137</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.008270148187875748</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.7305525089137</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.00736549124121666</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.7305525089137</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.009482458233833313</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.7305525089137</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.006964625790715218</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.011435059777391</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.003297038376331329</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.2923176106410809</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.005611110478639603</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.0155537985265255</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.03255591168999672</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.06069410219788551</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-8.570292203873397e-05</v>
+        <v>-7.719068296707701e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09845619665895525</v>
+        <v>-0.08867726889193431</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.06605508923530579</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.09854189958099392</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.04307224601507187</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.09854189958099392</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.03044035658240318</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.09854189958099392</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.02006915584206581</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.09854189958099392</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.01720328070223331</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.09854189958099392</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.009335391223430634</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.09854189958099392</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.009489848278462887</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.09854189958099392</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.007727863267064095</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.09854189958099392</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.008762059733271599</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.09854189958099392</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.009038744494318962</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.09854189958099392</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.009771022014319897</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.09854189958099392</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.009884580038487911</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.09854189958099392</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.01161793991923332</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.09854189958099392</v>
+        <v>-0.08875445957490138</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.02186392061412334</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.09861779246388865</v>
+        <v>-0.0888428258004114</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2728932662517455</v>
+        <v>0.3177448223563752</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.03310970962047577</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4476932195827002</v>
+        <v>0.5472569006066802</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01944362451114522</v>
+        <v>0.02263921529421907</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.02528779022395611</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2132489372843481</v>
+        <v>0.2742808846022973</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0340973642194692</v>
+        <v>0.03970159828710793</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.02524582296609879</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.261993809362548</v>
+        <v>0.331037237453491</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.04142458244643064</v>
+        <v>0.04823275319728687</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.0279815811663866</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.310742108989852</v>
+        <v>0.3877973679328209</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0109615360033033</v>
+        <v>0.01276342996409287</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01492760702967644</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2911883221077285</v>
+        <v>0.3650302245899483</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.006088019655193326</v>
+        <v>0.007089214900799215</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.02463622577488422</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2923937901453558</v>
+        <v>0.3664346315481942</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01279489493884663</v>
+        <v>0.01489892391181456</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.04314057901501656</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.3119021935583558</v>
+        <v>0.3891506211436058</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.005023377688153793</v>
+        <v>0.00584932989993628</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.02784911170601845</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.3091440046060139</v>
+        <v>0.3859398676240335</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003575965340619859</v>
+        <v>0.004164168221713969</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0166508499532938</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.3112704624351687</v>
+        <v>0.3884169493346468</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001404491064401727</v>
+        <v>0.001636690459404324</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.01141059957444668</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.3105006922323729</v>
+        <v>0.3875211909770556</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0007949934336779145</v>
+        <v>0.0009260135528737193</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01311550661921501</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.3106853667138552</v>
+        <v>0.3877371134224343</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000299161630746566</v>
+        <v>0.00034965950766588</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01796650886535645</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.3104892321718118</v>
+        <v>0.387509307129594</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001381248576441024</v>
+        <v>0.000161245026955842</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.02163166366517544</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.3</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.3104649286955984</v>
+        <v>0.3874818119025473</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.747614413300833e-05</v>
+        <v>5.635672237090206e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.03130625933408737</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.3104216360649285</v>
+        <v>0.3874320389805334</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.026354405308807e-05</v>
+        <v>1.312545856304208e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.02945829927921295</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.3103951143686669</v>
+        <v>0.3874018747157289</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>2.631772026544036e-06</v>
+        <v>4.062729281521043e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.02022183686494827</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.3103901024543941</v>
+        <v>0.3873968605675301</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-8.904788376657899e-07</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01174493692815304</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.3103857208688334</v>
+        <v>0.3873925516902127</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.211151546177397e-06</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.002781081944704056</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.3103823705140406</v>
+        <v>0.3873893840686479</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01283321529626846</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.3103770011870528</v>
+        <v>0.3873840147416601</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01717348396778107</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.3103710084536225</v>
+        <v>0.3873780220082297</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.01478111837059259</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.3103656406650441</v>
+        <v>0.3873726542196513</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.01259067002683878</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.3103656774135358</v>
+        <v>0.387372690968143</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.0072953961789608</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.3103657876590113</v>
+        <v>0.3873728012136186</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.000967489555478096</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.310365861155995</v>
+        <v>0.3873728747106022</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.009871754795312881</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.3103660448984541</v>
+        <v>0.3873730584530614</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.00245971605181694</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.011435059777391</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.3103675883351106</v>
+        <v>0.3873746018897178</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.0700334757566452</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.011435059777391</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.3103690582747837</v>
+        <v>0.3873760718293909</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.1361223459243774</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.011435059777391</v>
+        <v>-0.16</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.3103703077235057</v>
+        <v>0.3873773212781129</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.08984270691871643</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.2923176106410809</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.3103716674177029</v>
+        <v>0.3873786809723103</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.1372374296188354</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4267998384952287</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.3103694625081937</v>
+        <v>0.387376476062801</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.1324389278888702</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.3103690582747837</v>
+        <v>0.3873760718293909</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.08930964767932892</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.3103682130594717</v>
+        <v>0.387375226614079</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.04809883236885071</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.310368764286849</v>
+        <v>0.3873757778414562</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.01983563229441643</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.3103684335504225</v>
+        <v>0.3873754471050299</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.001422271132469177</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.310368139562488</v>
+        <v>0.3873751531170954</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.007140880450606346</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.09231761064108085</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.3103682130594717</v>
+        <v>0.387375226614079</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.0007510408759117126</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.011435059777391</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.3103677720775697</v>
+        <v>0.387374785632177</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.003111168742179871</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.7305525089137</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.3103676618320942</v>
+        <v>0.3873746753867015</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.003788234665989876</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.011435059777391</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.3103676250836025</v>
+        <v>0.3873746386382098</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01044687815010548</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.2923176106410809</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.3103677720775697</v>
+        <v>0.387374785632177</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.02624809928238392</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.4267998384952287</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.3103672943471761</v>
+        <v>0.3873743079017834</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.04443201422691345</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.3103682498079634</v>
+        <v>0.3873752633625707</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.02874818444252014</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.3103682130594717</v>
+        <v>0.387375226614079</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.00625292956829071</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.09231761064108085</v>
+        <v>-0.3</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.3103678823230453</v>
+        <v>0.3873748958776526</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.003685656934976578</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.09231761064108088</v>
+        <v>-0.16</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.3103683233049472</v>
+        <v>0.3873753368595545</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.00580378994345665</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.09231761064108088</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.3103676985805861</v>
+        <v>0.3873747121351934</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01524756755679846</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.3</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.310367514838127</v>
+        <v>0.3873745283927342</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.03785275295376778</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.3103671106047169</v>
+        <v>0.3873741241593242</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.04437763243913651</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.310366265389405</v>
+        <v>0.3873732789440122</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.02868778631091118</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.3103662286409133</v>
+        <v>0.3873732421955206</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.02440370433032513</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.3103663756348805</v>
+        <v>0.3873733891894878</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01405530795454979</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.3103663021378969</v>
+        <v>0.3873733156925042</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.02860569208860397</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.3103663756348805</v>
+        <v>0.3873733891894878</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.02208647131919861</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.3103664123833724</v>
+        <v>0.3873734259379797</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.01366991177201271</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.3103663021378969</v>
+        <v>0.3873733156925042</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.006706595420837402</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.3103667431197988</v>
+        <v>0.3873737566744061</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.005108749493956566</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.3103666328743233</v>
+        <v>0.3873736464289306</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003197859972715378</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.3103665961258313</v>
+        <v>0.3873736096804387</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.01057820860296488</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.3103665226288477</v>
+        <v>0.387373536183455</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.01593170873820782</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6267998384952288</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.310366485880356</v>
+        <v>0.3873734994349634</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.0174301415681839</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.310366265389405</v>
+        <v>0.3873732789440122</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.02108772657811642</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.3103661918924213</v>
+        <v>0.3873732054470286</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.01585503853857517</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.3103661183954377</v>
+        <v>0.387373131950045</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01531123835593462</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.3103661551439296</v>
+        <v>0.3873731686985369</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.01229317486286163</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.3103660448984541</v>
+        <v>0.3873730584530614</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.0190451554954052</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.6500000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.3103661551439296</v>
+        <v>0.3873731686985369</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.02087664790451527</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6267998384952288</v>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.3103664491318641</v>
+        <v>0.3873734626864714</v>
       </c>
     </row>
   </sheetData>
